--- a/scripts/checks/results/HLR_results_12_Dunn_fams_Famfirst_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_12_Dunn_fams_Famfirst_tPBC.xlsx
@@ -553,66 +553,66 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>539</v>
+        <v>662</v>
       </c>
       <c r="E2" t="n">
-        <v>537</v>
+        <v>660</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3002424530370029</v>
+        <v>0.2235251913827403</v>
       </c>
       <c r="H2" t="n">
-        <v>230.4086579424865</v>
+        <v>189.9953799857627</v>
       </c>
       <c r="I2" t="n">
-        <v>1.460779915114385e-43</v>
+        <v>3.606805372741333e-38</v>
       </c>
       <c r="J2" t="n">
-        <v>71.15456703886447</v>
+        <v>91.34369889831773</v>
       </c>
       <c r="K2" t="n">
-        <v>101.6846011131726</v>
+        <v>117.6389728096677</v>
       </c>
       <c r="L2" t="n">
-        <v>30.53003407430809</v>
+        <v>26.29527391134995</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1325038492343845</v>
+        <v>0.1383995437853299</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1890048347828486</v>
+        <v>0.1779712145380752</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.8158622228498638, 'N1ratio-ArgsPreds': -0.23974231781280247}</t>
+          <t>{'const': 0.6122542310653039, 'N1ratio-ArgsPreds': -2.3586335149019666}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 3.861723678139761e-68, 'N1ratio-ArgsPreds': 1.4607799151140621e-43}</t>
+          <t>{'const': 7.046203500856338e-68, 'N1ratio-ArgsPreds': 3.606805372740735e-38}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5479438411342928}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47278450839969377}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5479438411342936)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4727845083996953)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5479438411342935)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4727845083996953)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(30.024245303700386)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.352519138274157)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -632,76 +632,76 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>539</v>
+        <v>662</v>
       </c>
       <c r="E3" t="n">
-        <v>536</v>
+        <v>659</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3677103009192324</v>
+        <v>0.3226902160246737</v>
       </c>
       <c r="H3" t="n">
-        <v>155.8563436817371</v>
+        <v>156.9834493694593</v>
       </c>
       <c r="I3" t="n">
-        <v>4.420959780259847e-54</v>
+        <v>1.755624193101927e-56</v>
       </c>
       <c r="J3" t="n">
-        <v>64.29412583899577</v>
+        <v>79.67802726079529</v>
       </c>
       <c r="K3" t="n">
-        <v>101.6846011131726</v>
+        <v>117.6389728096677</v>
       </c>
       <c r="L3" t="n">
-        <v>18.6952376370884</v>
+        <v>18.98047277443619</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1199517273115593</v>
+        <v>0.1209074768752584</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1890048347828486</v>
+        <v>0.1779712145380752</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.9279371858966083, 'N1ratio-ArgsPreds': -0.2281861069604998, 'Fam_class': -0.0038435901923523676}</t>
+          <t>{'const': 0.7605153950917698, 'N1ratio-ArgsPreds': -2.2157716072717006, 'Fam_class': -0.003999273368872975}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 8.445221960703667e-80, 'N1ratio-ArgsPreds': 3.2528421283290984e-43, 'Fam_class': 1.727350341704145e-13}</t>
+          <t>{'const': 2.8545825977272187e-87, 'N1ratio-ArgsPreds': 3.175014812446558e-38, 'Fam_class': 2.411584701137712e-21}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5215315055018624, 'Fam_class': -0.2610851572874029}</t>
+          <t>{'N1ratio-ArgsPreds': -0.444148055834563, 'Fam_class': -0.3162041604050294}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5464666253104042), 'Fam_class': np.float64(-0.31050931488820976)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47341546024328685), 'Fam_class': np.float64(-0.35736793026027425)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5188559421197032), 'Fam_class': np.float64(-0.2597457369856707)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4423229238197559), 'Fam_class': np.float64(-0.31490478662912325)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(26.921148867292484), 'Fam_class': np.float64(6.746784788222923)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.56495689364576), 'Fam_class': np.float64(9.916502464193364)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.06746784788222948</v>
+        <v>0.09916502464193344</v>
       </c>
       <c r="V3" t="n">
-        <v>57.19335063887485</v>
+        <v>96.48428648923041</v>
       </c>
       <c r="W3" t="n">
-        <v>1.727350341703133e-13</v>
+        <v>2.411584701138846e-21</v>
       </c>
     </row>
     <row r="4">
@@ -713,80 +713,80 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'Fam_class', 'latitude', 'longitude', 'Macro_class']</t>
+          <t>['N1ratio-ArgsPreds', 'Fam_class', 'Macro_class']</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>539</v>
+        <v>662</v>
       </c>
       <c r="E4" t="n">
-        <v>533</v>
+        <v>658</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4308967329877672</v>
+        <v>0.3574609078035639</v>
       </c>
       <c r="H4" t="n">
-        <v>80.71222640777539</v>
+        <v>122.020735231695</v>
       </c>
       <c r="I4" t="n">
-        <v>5.384584677552566e-63</v>
+        <v>7.732030001274338e-63</v>
       </c>
       <c r="J4" t="n">
-        <v>57.86903869834223</v>
+        <v>75.5876387960451</v>
       </c>
       <c r="K4" t="n">
-        <v>101.6846011131726</v>
+        <v>117.6389728096677</v>
       </c>
       <c r="L4" t="n">
-        <v>8.763112482966067</v>
+        <v>14.01711133787419</v>
       </c>
       <c r="M4" t="n">
-        <v>0.108572305250173</v>
+        <v>0.114874830997029</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1890048347828486</v>
+        <v>0.1779712145380752</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.6961464576636529, 'N1ratio-ArgsPreds': -0.23408053508169102, 'Fam_class': -0.0017571297445560282, 'latitude': 0.003932715362527442, 'longitude': -6.492392921287051e-05, 'Macro_class': 0.0582735695555292}</t>
+          <t>{'const': 0.4270272555566394, 'N1ratio-ArgsPreds': -2.1957685438173153, 'Fam_class': -0.0008073176147423974, 'Macro_class': 0.07834611680144354}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 1.2854831552066137e-13, 'N1ratio-ArgsPreds': 3.562251281801858e-47, 'Fam_class': 0.11769560292191082, 'latitude': 2.383367421084865e-06, 'longitude': 0.8596779117769799, 'Macro_class': 3.455875400858264e-05}</t>
+          <t>{'const': 6.983427456001168e-11, 'N1ratio-ArgsPreds': 2.7849527092732195e-39, 'Fam_class': 0.225916988859383, 'Macro_class': 3.944167911358861e-09}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5350035350354113, 'Fam_class': -0.11935728648818633, 'latitude': 0.1766809503707978, 'longitude': -0.010849393119779683, 'Macro_class': 0.22141500790721205}</t>
+          <t>{'N1ratio-ArgsPreds': -0.44013847212347834, 'Fam_class': -0.06383089251579463, 'Macro_class': 0.3141055853774373}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5687521701947307), 'Fam_class': np.float64(-0.06772080829358151), 'latitude': np.float64(0.2023308348775356), 'longitude': np.float64(-0.007660853127790907), 'Macro_class': np.float64(0.17802132246872537)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47969635395304844), 'Fam_class': np.float64(-0.04719911699693482), 'Macro_class': np.float64(0.22657552294544023)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5216485146302998), 'Fam_class': np.float64(-0.05120540714737771), 'latitude': np.float64(0.15585983719915592), 'longitude': np.float64(-0.005779435483903714), 'Macro_class': np.float64(0.13647739071120063)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4382293480554757), 'Fam_class': np.float64(-0.03787633442411308), 'Macro_class': np.float64(0.18646901023729165)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(27.21171728159981), 'Fam_class': np.float64(0.26219937211287203), 'latitude': np.float64(2.4292288851747386), 'longitude': np.float64(0.0033401874512605356), 'Macro_class': np.float64(1.862607817533771)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.20449614971273), 'Fam_class': np.float64(0.14346167094072537), 'Macro_class': np.float64(3.477069177887518)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.0631864320685348</v>
+        <v>0.03477069177889014</v>
       </c>
       <c r="V4" t="n">
-        <v>19.72598544920152</v>
+        <v>35.60735131663419</v>
       </c>
       <c r="W4" t="n">
-        <v>3.865301959232984e-12</v>
+        <v>3.944167911359021e-09</v>
       </c>
     </row>
     <row r="5">
@@ -798,80 +798,80 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'Fam_class', 'latitude', 'longitude', 'Macro_class', 'Nlen_freq', 'Vlen_freq']</t>
+          <t>['N1ratio-ArgsPreds', 'Fam_class', 'Macro_class', 'Nlen_freq', 'Vlen_freq']</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>539</v>
+        <v>662</v>
       </c>
       <c r="E5" t="n">
-        <v>531</v>
+        <v>656</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4605058979068151</v>
+        <v>0.385597461649784</v>
       </c>
       <c r="H5" t="n">
-        <v>64.75077586305164</v>
+        <v>82.34078443799432</v>
       </c>
       <c r="I5" t="n">
-        <v>3.55672114852878e-67</v>
+        <v>4.442106470942249e-67</v>
       </c>
       <c r="J5" t="n">
-        <v>54.8582425742547</v>
+        <v>72.27768350317186</v>
       </c>
       <c r="K5" t="n">
-        <v>101.6846011131726</v>
+        <v>117.6389728096677</v>
       </c>
       <c r="L5" t="n">
-        <v>6.68947979127398</v>
+        <v>9.072257861299164</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1033111912886153</v>
+        <v>0.1101793955841034</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1890048347828486</v>
+        <v>0.1779712145380752</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.3013014345823378, 'N1ratio-ArgsPreds': -0.21875285042968165, 'Fam_class': -0.004469086952158842, 'latitude': 0.0038626991338975565, 'longitude': -0.0005816308890785851, 'Macro_class': 0.03965047136416293, 'Nlen_freq': 0.047799212071236837, 'Vlen_freq': 0.03496604140457699}</t>
+          <t>{'const': 0.18015827901476877, 'N1ratio-ArgsPreds': -2.0797628700318613, 'Fam_class': -0.0018767080107926757, 'Macro_class': 0.06845659271188573, 'Nlen_freq': 0.28074866988727665, 'Vlen_freq': 0.5450644056063416}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 0.011672733542979206, 'N1ratio-ArgsPreds': 9.545059203789041e-42, 'Fam_class': 0.00025068224571369804, 'latitude': 2.1179641117541315e-06, 'longitude': 0.1172072374136293, 'Macro_class': 0.005383749551476428, 'Nlen_freq': 0.07177602002568507, 'Vlen_freq': 0.06612207205839789}</t>
+          <t>{'const': 0.022096224750881792, 'N1ratio-ArgsPreds': 7.754248197618575e-36, 'Fam_class': 0.007349213594939344, 'Macro_class': 2.89019315308934e-07, 'Nlen_freq': 0.23864917337601455, 'Vlen_freq': 0.013544549634792012}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4999712950848694, 'Fam_class': -0.3035735370948469, 'latitude': 0.17353540520025768, 'longitude': -0.09719593750295662, 'Macro_class': 0.15065508252853915, 'Nlen_freq': 0.10205990338527446, 'Vlen_freq': 0.10161364849679308}</t>
+          <t>{'N1ratio-ArgsPreds': -0.41688531087324027, 'Fam_class': -0.14838267508713013, 'Macro_class': 0.27445646325020523, 'Nlen_freq': 0.06147936684426135, 'Vlen_freq': 0.12586307125780938}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5404188496267708), 'Fam_class': np.float64(-0.15797378583359561), 'latitude': np.float64(0.20371213287094686), 'longitude': np.float64(-0.06793824368415065), 'Macro_class': np.float64(0.12039455798132674), 'Nlen_freq': np.float64(0.07805411206409636), 'Vlen_freq': np.float64(0.07965558414267293)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46042737674515494), 'Fam_class': np.float64(-0.10441310382752554), 'Macro_class': np.float64(0.19839239081483445), 'Nlen_freq': np.float64(0.0460007853659187), 'Vlen_freq': np.float64(0.09621588418462351)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47176239891949084), 'Fam_class': np.float64(-0.11750766774176961), 'latitude': np.float64(0.15283185281611816), 'longitude': np.float64(-0.05001637956246471), 'Macro_class': np.float64(0.08907806162429423), 'Nlen_freq': np.float64(0.057506394876041846), 'Vlen_freq': np.float64(0.05869373797894043)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.40655817977576597), 'Fam_class': np.float64(-0.08229280502384366), 'Macro_class': np.float64(0.1586613242731975), 'Nlen_freq': np.float64(0.036095389546927086), 'Vlen_freq': np.float64(0.07576923079817192)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.255976103427283), 'Fam_class': np.float64(1.3808051978110123), 'latitude': np.float64(2.3357575235207606), 'longitude': np.float64(0.25016382245365376), 'Macro_class': np.float64(0.793490106274156), 'Nlen_freq': np.float64(0.33069854516392516), 'Vlen_freq': np.float64(0.3444954877940514)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(16.528955354258404), 'Fam_class': np.float64(0.6772105758692348), 'Macro_class': np.float64(2.5173415820124734), 'Nlen_freq': np.float64(0.1302877146544413), 'Vlen_freq': np.float64(0.5740976335746645)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.02960916491904786</v>
+        <v>0.02813655384622016</v>
       </c>
       <c r="V5" t="n">
-        <v>14.5714906900861</v>
+        <v>15.0207544492593</v>
       </c>
       <c r="W5" t="n">
-        <v>6.906177973553962e-07</v>
+        <v>4.183408356918715e-07</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_12_Dunn_fams_Famfirst_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_12_Dunn_fams_Famfirst_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2235251913827403</v>
+        <v>0.2127090200070492</v>
       </c>
       <c r="H2" t="n">
-        <v>189.9953799857627</v>
+        <v>178.3177462618833</v>
       </c>
       <c r="I2" t="n">
-        <v>3.606805372741333e-38</v>
+        <v>3.551046890077052e-36</v>
       </c>
       <c r="J2" t="n">
-        <v>91.34369889831773</v>
+        <v>92.1915359049147</v>
       </c>
       <c r="K2" t="n">
-        <v>117.6389728096677</v>
+        <v>117.0996978851963</v>
       </c>
       <c r="L2" t="n">
-        <v>26.29527391134995</v>
+        <v>24.90816198028165</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1383995437853299</v>
+        <v>0.1396841453104768</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1779712145380752</v>
+        <v>0.1771553674511291</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.6122542310653039, 'N1ratio-ArgsPreds': -2.3586335149019666}</t>
+          <t>{'const': 0.5881292512992626, 'N1ratio-ArgsPreds': -2.1993804205042555}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 7.046203500856338e-68, 'N1ratio-ArgsPreds': 3.606805372740735e-38}</t>
+          <t>{'const': 5.747937176790004e-66, 'N1ratio-ArgsPreds': 3.551046890075819e-36}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.47278450839969377}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4612038811708435}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4727845083996953)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4612038811708424)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4727845083996953)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46120388117084227)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.352519138274157)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.27090200070484)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3226902160246737</v>
+        <v>0.3143479930593552</v>
       </c>
       <c r="H3" t="n">
-        <v>156.9834493694593</v>
+        <v>151.0644797427451</v>
       </c>
       <c r="I3" t="n">
-        <v>1.755624193101927e-56</v>
+        <v>9.912567001865083e-55</v>
       </c>
       <c r="J3" t="n">
-        <v>79.67802726079529</v>
+        <v>80.28964286712805</v>
       </c>
       <c r="K3" t="n">
-        <v>117.6389728096677</v>
+        <v>117.0996978851963</v>
       </c>
       <c r="L3" t="n">
-        <v>18.98047277443619</v>
+        <v>18.40502750903415</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1209074768752584</v>
+        <v>0.1218355733947315</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1779712145380752</v>
+        <v>0.1771553674511291</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.7605153950917698, 'N1ratio-ArgsPreds': -2.2157716072717006, 'Fam_class': -0.003999273368872975}</t>
+          <t>{'const': 0.7394023249328201, 'N1ratio-ArgsPreds': -2.0659477516740434, 'Fam_class': -0.004038426249780229}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 2.8545825977272187e-87, 'N1ratio-ArgsPreds': 3.175014812446558e-38, 'Fam_class': 2.411584701137712e-21}</t>
+          <t>{'const': 1.4637857582528483e-85, 'N1ratio-ArgsPreds': 2.738826339175663e-36, 'Fam_class': 1.4195739528652064e-21}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.444148055834563, 'Fam_class': -0.3162041604050294}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4332234262364632, 'Fam_class': -0.3200341839720246}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47341546024328685), 'Fam_class': np.float64(-0.35736793026027425)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46218131171638166), 'Fam_class': np.float64(-0.3593043675180531)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4423229238197559), 'Fam_class': np.float64(-0.31490478662912325)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4315644847816254), 'Fam_class': np.float64(-0.3188086778183845)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(19.56495689364576), 'Fam_class': np.float64(9.916502464193364)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(18.62479045248298), 'Fam_class': np.float64(10.16389730523065)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.09916502464193344</v>
+        <v>0.1016389730523061</v>
       </c>
       <c r="V3" t="n">
-        <v>96.48428648923041</v>
+        <v>97.68816041293671</v>
       </c>
       <c r="W3" t="n">
-        <v>2.411584701138846e-21</v>
+        <v>1.419573952864477e-21</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3574609078035639</v>
+        <v>0.3489660847113103</v>
       </c>
       <c r="H4" t="n">
-        <v>122.020735231695</v>
+        <v>117.566677837473</v>
       </c>
       <c r="I4" t="n">
-        <v>7.732030001274338e-63</v>
+        <v>5.751093629366023e-61</v>
       </c>
       <c r="J4" t="n">
-        <v>75.5876387960451</v>
+        <v>76.23587479332208</v>
       </c>
       <c r="K4" t="n">
-        <v>117.6389728096677</v>
+        <v>117.0996978851963</v>
       </c>
       <c r="L4" t="n">
-        <v>14.01711133787419</v>
+        <v>13.62127436395809</v>
       </c>
       <c r="M4" t="n">
-        <v>0.114874830997029</v>
+        <v>0.1158599920871156</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1779712145380752</v>
+        <v>0.1771553674511291</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.4270272555566394, 'N1ratio-ArgsPreds': -2.1957685438173153, 'Fam_class': -0.0008073176147423974, 'Macro_class': 0.07834611680144354}</t>
+          <t>{'const': 0.4056495142369452, 'N1ratio-ArgsPreds': -2.035472342974993, 'Fam_class': -0.0008621371006486907, 'Macro_class': 0.07802237381601512}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 6.983427456001168e-11, 'N1ratio-ArgsPreds': 2.7849527092732195e-39, 'Fam_class': 0.225916988859383, 'Macro_class': 3.944167911358861e-09}</t>
+          <t>{'const': 6.349502533640233e-10, 'N1ratio-ArgsPreds': 6.964604526933164e-37, 'Fam_class': 0.19772957215448503, 'Macro_class': 5.33233767609879e-09}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.44013847212347834, 'Fam_class': -0.06383089251579463, 'Macro_class': 0.3141055853774373}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4268328188448382, 'Fam_class': -0.06832199634526596, 'Macro_class': 0.31352708698927645}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47969635395304844), 'Fam_class': np.float64(-0.04719911699693482), 'Macro_class': np.float64(0.22657552294544023)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.465989409649706), 'Fam_class': np.float64(-0.05020070991952687), 'Macro_class': np.float64(0.22469824786382533)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4382293480554757), 'Fam_class': np.float64(-0.03787633442411308), 'Macro_class': np.float64(0.18646901023729165)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4249496756408016), 'Fam_class': np.float64(-0.040556418090922676), 'Macro_class': np.float64(0.18605937668379074)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(19.20449614971273), 'Fam_class': np.float64(0.14346167094072537), 'Macro_class': np.float64(3.477069177887518)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(18.05822268272225), 'Fam_class': np.float64(0.16448230483657203), 'Macro_class': np.float64(3.4618091651960734)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.03477069177889014</v>
+        <v>0.03461809165195506</v>
       </c>
       <c r="V4" t="n">
-        <v>35.60735131663419</v>
+        <v>34.98850639276697</v>
       </c>
       <c r="W4" t="n">
-        <v>3.944167911359021e-09</v>
+        <v>5.33233767609933e-09</v>
       </c>
     </row>
     <row r="5">
@@ -811,67 +811,67 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.385597461649784</v>
+        <v>0.3769932747413847</v>
       </c>
       <c r="H5" t="n">
-        <v>82.34078443799432</v>
+        <v>79.39162715384457</v>
       </c>
       <c r="I5" t="n">
-        <v>4.442106470942249e-67</v>
+        <v>4.111853450219204e-65</v>
       </c>
       <c r="J5" t="n">
-        <v>72.27768350317186</v>
+        <v>72.95389930822938</v>
       </c>
       <c r="K5" t="n">
-        <v>117.6389728096677</v>
+        <v>117.0996978851963</v>
       </c>
       <c r="L5" t="n">
-        <v>9.072257861299164</v>
+        <v>8.829159715393393</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1101793955841034</v>
+        <v>0.1112102123601058</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1779712145380752</v>
+        <v>0.1771553674511291</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.18015827901476877, 'N1ratio-ArgsPreds': -2.0797628700318613, 'Fam_class': -0.0018767080107926757, 'Macro_class': 0.06845659271188573, 'Nlen_freq': 0.28074866988727665, 'Vlen_freq': 0.5450644056063416}</t>
+          <t>{'const': 0.1687781245109799, 'N1ratio-ArgsPreds': -1.9029454343513557, 'Fam_class': -0.0018260318800263774, 'Macro_class': 0.06996385328613082, 'Nlen_freq': 0.1350375345436348, 'Vlen_freq': 0.6579628576506252}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 0.022096224750881792, 'N1ratio-ArgsPreds': 7.754248197618575e-36, 'Fam_class': 0.007349213594939344, 'Macro_class': 2.89019315308934e-07, 'Nlen_freq': 0.23864917337601455, 'Vlen_freq': 0.013544549634792012}</t>
+          <t>{'const': 0.03291289784754368, 'N1ratio-ArgsPreds': 6.894642942630795e-33, 'Fam_class': 0.009448045664352556, 'Macro_class': 1.7919022379768589e-07, 'Nlen_freq': 0.56782047116712, 'Vlen_freq': 0.0026973691353908203}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.41688531087324027, 'Fam_class': -0.14838267508713013, 'Macro_class': 0.27445646325020523, 'Nlen_freq': 0.06147936684426135, 'Vlen_freq': 0.12586307125780938}</t>
+          <t>{'N1ratio-ArgsPreds': -0.39904229927533974, 'Fam_class': -0.1447080091317617, 'Macro_class': 0.28114452358335124, 'Nlen_freq': 0.029807946664035908, 'Vlen_freq': 0.15311241881719465}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46042737674515494), 'Fam_class': np.float64(-0.10441310382752554), 'Macro_class': np.float64(0.19839239081483445), 'Nlen_freq': np.float64(0.0460007853659187), 'Vlen_freq': np.float64(0.09621588418462351)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4422750689855661), 'Fam_class': np.float64(-0.10111212424105663), 'Macro_class': np.float64(0.20177314850356579), 'Nlen_freq': np.float64(0.02230984970239089), 'Vlen_freq': np.float64(0.1167844522911972)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.40655817977576597), 'Fam_class': np.float64(-0.08229280502384366), 'Macro_class': np.float64(0.1586613242731975), 'Nlen_freq': np.float64(0.036095389546927086), 'Vlen_freq': np.float64(0.07576923079817192)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.38922860425436884), 'Fam_class': np.float64(-0.08021970641369203), 'Macro_class': np.float64(0.1626055346455999), 'Nlen_freq': np.float64(0.017613721265249755), 'Vlen_freq': np.float64(0.09281397296439804)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(16.528955354258404), 'Fam_class': np.float64(0.6772105758692348), 'Macro_class': np.float64(2.5173415820124734), 'Nlen_freq': np.float64(0.1302877146544413), 'Vlen_freq': np.float64(0.5740976335746645)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(15.149890636980407), 'Fam_class': np.float64(0.6435201297098941), 'Macro_class': np.float64(2.644055989738139), 'Nlen_freq': np.float64(0.03102431768099114), 'Vlen_freq': np.float64(0.861443357743601)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.02813655384622016</v>
+        <v>0.02802719003007437</v>
       </c>
       <c r="V5" t="n">
-        <v>15.0207544492593</v>
+        <v>14.75572888245843</v>
       </c>
       <c r="W5" t="n">
-        <v>4.183408356918715e-07</v>
+        <v>5.390534006316035e-07</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_12_Dunn_fams_Famfirst_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_12_Dunn_fams_Famfirst_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2127090200070492</v>
+        <v>0.2126104794529781</v>
       </c>
       <c r="H2" t="n">
-        <v>178.3177462618833</v>
+        <v>178.2128321208532</v>
       </c>
       <c r="I2" t="n">
-        <v>3.551046890077052e-36</v>
+        <v>3.701627190479354e-36</v>
       </c>
       <c r="J2" t="n">
-        <v>92.1915359049147</v>
+        <v>92.20307497402587</v>
       </c>
       <c r="K2" t="n">
         <v>117.0996978851963</v>
       </c>
       <c r="L2" t="n">
-        <v>24.90816198028165</v>
+        <v>24.89662291117048</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1396841453104768</v>
+        <v>0.139701628748524</v>
       </c>
       <c r="N2" t="n">
         <v>0.1771553674511291</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5881292512992626, 'N1ratio-ArgsPreds': -2.1993804205042555}</t>
+          <t>{'const': 0.5877559712647106, 'N1ratio-ArgsPreds': -2.1955128851816026}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 5.747937176790004e-66, 'N1ratio-ArgsPreds': 3.551046890075819e-36}</t>
+          <t>{'const': 5.84595231215245e-66, 'N1ratio-ArgsPreds': 3.701627190478273e-36}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4612038811708435}</t>
+          <t>{'N1ratio-ArgsPreds': -0.46109703908502636}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4612038811708424)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4610970390850252)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46120388117084227)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46109703908502514)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.27090200070484)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.26104794529772)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3143479930593552</v>
+        <v>0.3142536789280335</v>
       </c>
       <c r="H3" t="n">
-        <v>151.0644797427451</v>
+        <v>150.9983852992777</v>
       </c>
       <c r="I3" t="n">
-        <v>9.912567001865083e-55</v>
+        <v>1.037214918238356e-54</v>
       </c>
       <c r="J3" t="n">
-        <v>80.28964286712805</v>
+        <v>80.30068702341214</v>
       </c>
       <c r="K3" t="n">
         <v>117.0996978851963</v>
       </c>
       <c r="L3" t="n">
-        <v>18.40502750903415</v>
+        <v>18.39950543089211</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1218355733947315</v>
+        <v>0.1218523323572263</v>
       </c>
       <c r="N3" t="n">
         <v>0.1771553674511291</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.7394023249328201, 'N1ratio-ArgsPreds': -2.0659477516740434, 'Fam_class': -0.004038426249780229}</t>
+          <t>{'const': 0.7390483146626645, 'N1ratio-ArgsPreds': -2.0622715113437615, 'Fam_class': -0.004038512462715218}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 1.4637857582528483e-85, 'N1ratio-ArgsPreds': 2.738826339175663e-36, 'Fam_class': 1.4195739528652064e-21}</t>
+          <t>{'const': 1.5006787508941505e-85, 'N1ratio-ArgsPreds': 2.8665240304344807e-36, 'Fam_class': 1.425438616316008e-21}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4332234262364632, 'Fam_class': -0.3200341839720246}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4331139635244528, 'Fam_class': -0.3200410161102365}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46218131171638166), 'Fam_class': np.float64(-0.3593043675180531)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4620642748324306), 'Fam_class': np.float64(-0.35928935350513513)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4315644847816254), 'Fam_class': np.float64(-0.3188086778183845)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.43145520091141415), 'Fam_class': np.float64(-0.31881530621200665)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(18.62479045248298), 'Fam_class': np.float64(10.16389730523065)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(18.615359039350878), 'Fam_class': np.float64(10.164319947505557)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.1016389730523061</v>
+        <v>0.1016431994750554</v>
       </c>
       <c r="V3" t="n">
-        <v>97.68816041293671</v>
+        <v>97.67878644883304</v>
       </c>
       <c r="W3" t="n">
-        <v>1.419573952864477e-21</v>
+        <v>1.425438616308688e-21</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3489660847113103</v>
+        <v>0.3490950222132244</v>
       </c>
       <c r="H4" t="n">
-        <v>117.566677837473</v>
+        <v>117.633414223455</v>
       </c>
       <c r="I4" t="n">
-        <v>5.751093629366023e-61</v>
+        <v>5.389260241342766e-61</v>
       </c>
       <c r="J4" t="n">
-        <v>76.23587479332208</v>
+        <v>76.22077625080186</v>
       </c>
       <c r="K4" t="n">
         <v>117.0996978851963</v>
       </c>
       <c r="L4" t="n">
-        <v>13.62127436395809</v>
+        <v>13.62630721146483</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1158599920871156</v>
+        <v>0.115837045973863</v>
       </c>
       <c r="N4" t="n">
         <v>0.1771553674511291</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.4056495142369452, 'N1ratio-ArgsPreds': -2.035472342974993, 'Fam_class': -0.0008621371006486907, 'Macro_class': 0.07802237381601512}</t>
+          <t>{'const': 0.4044321491783023, 'N1ratio-ArgsPreds': -2.032995032838356, 'Fam_class': -0.0008518584602907637, 'Macro_class': 0.07826987988457677}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 6.349502533640233e-10, 'N1ratio-ArgsPreds': 6.964604526933164e-37, 'Fam_class': 0.19772957215448503, 'Macro_class': 5.33233767609879e-09}</t>
+          <t>{'const': 6.933091660414142e-10, 'N1ratio-ArgsPreds': 6.522930735819326e-37, 'Fam_class': 0.20308922670303675, 'Macro_class': 4.760692740799837e-09}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4268328188448382, 'Fam_class': -0.06832199634526596, 'Macro_class': 0.31352708698927645}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4269653785424238, 'Fam_class': -0.06750744233936574, 'Macro_class': 0.31452167165637834}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.465989409649706), 'Fam_class': np.float64(-0.05020070991952687), 'Macro_class': np.float64(0.22469824786382533)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4661557404946969), 'Fam_class': np.float64(-0.049607179321554805), 'Macro_class': np.float64(0.22540611933786894)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4249496756408016), 'Fam_class': np.float64(-0.040556418090922676), 'Macro_class': np.float64(0.18605937668379074)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.42510135771265123), 'Fam_class': np.float64(-0.04007175470900394), 'Macro_class': np.float64(0.18665835980530113)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(18.05822268272225), 'Fam_class': np.float64(0.16448230483657203), 'Macro_class': np.float64(3.4618091651960734)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(18.071116432913943), 'Fam_class': np.float64(0.16057455254585795), 'Macro_class': np.float64(3.484134328520525)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.03461809165195506</v>
+        <v>0.03484134328519095</v>
       </c>
       <c r="V4" t="n">
-        <v>34.98850639276697</v>
+        <v>35.22112238196102</v>
       </c>
       <c r="W4" t="n">
-        <v>5.33233767609933e-09</v>
+        <v>4.760692740800294e-09</v>
       </c>
     </row>
     <row r="5">
@@ -811,67 +811,67 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3769932747413847</v>
+        <v>0.3767743170609335</v>
       </c>
       <c r="H5" t="n">
-        <v>79.39162715384457</v>
+        <v>79.3176400646306</v>
       </c>
       <c r="I5" t="n">
-        <v>4.111853450219204e-65</v>
+        <v>4.610175050862153e-65</v>
       </c>
       <c r="J5" t="n">
-        <v>72.95389930822938</v>
+        <v>72.97953918645986</v>
       </c>
       <c r="K5" t="n">
         <v>117.0996978851963</v>
       </c>
       <c r="L5" t="n">
-        <v>8.829159715393393</v>
+        <v>8.824031739747298</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1112102123601058</v>
+        <v>0.1112492975403351</v>
       </c>
       <c r="N5" t="n">
         <v>0.1771553674511291</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.1687781245109799, 'N1ratio-ArgsPreds': -1.9029454343513557, 'Fam_class': -0.0018260318800263774, 'Macro_class': 0.06996385328613082, 'Nlen_freq': 0.1350375345436348, 'Vlen_freq': 0.6579628576506252}</t>
+          <t>{'const': 0.16925720430356392, 'N1ratio-ArgsPreds': -1.8994373463282157, 'Fam_class': -0.0018081729523967511, 'Macro_class': 0.07030723584394889, 'Nlen_freq': 0.13232433524992462, 'Vlen_freq': 0.6562458119930286}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 0.03291289784754368, 'N1ratio-ArgsPreds': 6.894642942630795e-33, 'Fam_class': 0.009448045664352556, 'Macro_class': 1.7919022379768589e-07, 'Nlen_freq': 0.56782047116712, 'Vlen_freq': 0.0026973691353908203}</t>
+          <t>{'const': 0.032396955824892236, 'N1ratio-ArgsPreds': 7.679828348118479e-33, 'Fam_class': 0.010171937807837877, 'Macro_class': 1.5609682226863143e-07, 'Nlen_freq': 0.5806061638562758, 'Vlen_freq': 0.0027840059113080563}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.39904229927533974, 'Fam_class': -0.1447080091317617, 'Macro_class': 0.28114452358335124, 'Nlen_freq': 0.029807946664035908, 'Vlen_freq': 0.15311241881719465}</t>
+          <t>{'N1ratio-ArgsPreds': -0.39891587165384174, 'Fam_class': -0.14329273818782065, 'Macro_class': 0.2825243807680288, 'Nlen_freq': 0.028860824051949223, 'Vlen_freq': 0.1528411389095693}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4422750689855661), 'Fam_class': np.float64(-0.10111212424105663), 'Macro_class': np.float64(0.20177314850356579), 'Nlen_freq': np.float64(0.02230984970239089), 'Vlen_freq': np.float64(0.1167844522911972)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4419777356899085), 'Fam_class': np.float64(-0.10012477268852586), 'Macro_class': np.float64(0.20273820006954038), 'Nlen_freq': np.float64(0.02157719208046599), 'Vlen_freq': np.float64(0.11641171137310075)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.38922860425436884), 'Fam_class': np.float64(-0.08021970641369203), 'Macro_class': np.float64(0.1626055346455999), 'Nlen_freq': np.float64(0.017613721265249755), 'Vlen_freq': np.float64(0.09281397296439804)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.38897171593447816), 'Fam_class': np.float64(-0.07944235206898324), 'Macro_class': np.float64(0.1634452212178025), 'Nlen_freq': np.float64(0.01703800418902348), 'Vlen_freq': np.float64(0.09252991807223523)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(15.149890636980407), 'Fam_class': np.float64(0.6435201297098941), 'Macro_class': np.float64(2.644055989738139), 'Nlen_freq': np.float64(0.03102431768099114), 'Vlen_freq': np.float64(0.861443357743601)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(15.129899579701236), 'Fam_class': np.float64(0.6311087302252286), 'Macro_class': np.float64(2.6714340338936395), 'Nlen_freq': np.float64(0.029029358674518165), 'Vlen_freq': np.float64(0.8561785738454566)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.02802719003007437</v>
+        <v>0.02767929484770904</v>
       </c>
       <c r="V5" t="n">
-        <v>14.75572888245843</v>
+        <v>14.56744957498199</v>
       </c>
       <c r="W5" t="n">
-        <v>5.390534006316035e-07</v>
+        <v>6.455082394067219e-07</v>
       </c>
     </row>
   </sheetData>
